--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling2020.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\Vanguard EU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48729FC4-570B-45E2-B22A-3125E79E7519}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17DD1F4-6117-4EB1-B882-574B5C81BA92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38535" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MarketCap" sheetId="7" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
   <si>
     <t>Kosten uit https://global.vanguard.com/portal/site/loadPDF?country=global&amp;docId=15835</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Vanguard FTSE All-World</t>
+  </si>
+  <si>
+    <t>TODO rente er uit?</t>
   </si>
 </sst>
 </file>
@@ -1031,6 +1034,9 @@
       <c r="H10" s="24"/>
       <c r="I10" s="24"/>
       <c r="J10" s="5"/>
+      <c r="M10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -1616,6 +1622,7 @@
         <f>0.22%-H14+J19-I29+I32+I23</f>
         <v>5.2401835962977376E-3</v>
       </c>
+      <c r="E41" s="4"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">

--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling2020.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\Vanguard EU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17DD1F4-6117-4EB1-B882-574B5C81BA92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2677A085-5C23-457B-AD71-35E3A5DEB25C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38535" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MarketCap" sheetId="7" r:id="rId1"/>
@@ -267,7 +267,7 @@
     <t>Vanguard FTSE All-World</t>
   </si>
   <si>
-    <t>TODO rente er uit?</t>
+    <t>Boekjaar anders dan kalenderjaar!</t>
   </si>
 </sst>
 </file>
@@ -757,15 +757,15 @@
       </c>
       <c r="C8" s="5">
         <f>VWRL!C41</f>
-        <v>5.2401835962977376E-3</v>
+        <v>5.3653646614683619E-3</v>
       </c>
       <c r="D8" s="5">
         <f>VWRL!C42</f>
-        <v>2.1316411736430033E-3</v>
+        <v>2.2568222388136272E-3</v>
       </c>
       <c r="E8" s="5">
         <f>VWRL!C45</f>
-        <v>4.8882888908656254E-3</v>
+        <v>4.9595663904319527E-3</v>
       </c>
       <c r="F8" s="6">
         <f>VWRL!J18</f>
@@ -785,7 +785,7 @@
       </c>
       <c r="C10" s="5">
         <f>D8+(F8*2.5%)</f>
-        <v>4.9872598700677444E-3</v>
+        <v>5.1124409352383687E-3</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
@@ -1148,10 +1148,7 @@
         <f t="shared" si="3"/>
         <v>2.34859072424947E-4</v>
       </c>
-      <c r="J14" s="4">
-        <f>AVERAGE(D14:I14)</f>
-        <v>7.3240871118377394E-5</v>
-      </c>
+      <c r="J14" s="4"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D15" s="19"/>
@@ -1362,10 +1359,7 @@
         <f t="shared" si="6"/>
         <v>3.3821162220955914E-6</v>
       </c>
-      <c r="J23" s="4">
-        <f>AVERAGE(D23:I23)</f>
-        <v>1.9337305514080175E-5</v>
-      </c>
+      <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="19"/>
@@ -1587,8 +1581,8 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <f>J7+J19-J29+J32-J14+J23</f>
-        <v>5.9518947054321104E-3</v>
+        <f>J7+J19-J29+J32</f>
+        <v>6.0057982710364074E-3</v>
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
@@ -1611,7 +1605,7 @@
       </c>
       <c r="C39" s="5">
         <f>C38-C37</f>
-        <v>-3.518947054321122E-4</v>
+        <v>-4.0579827103640921E-4</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
@@ -1619,8 +1613,8 @@
         <v>16</v>
       </c>
       <c r="C41" s="15">
-        <f>0.22%-H14+J19-I29+I32+I23</f>
-        <v>5.2401835962977376E-3</v>
+        <f>0.22%+J19-I29+I32</f>
+        <v>5.3653646614683619E-3</v>
       </c>
       <c r="E41" s="4"/>
     </row>
@@ -1629,8 +1623,8 @@
         <v>51</v>
       </c>
       <c r="C42" s="15">
-        <f>0.22%-H14-I29+I32+I23</f>
-        <v>2.1316411736430033E-3</v>
+        <f>C41-J19</f>
+        <v>2.2568222388136272E-3</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
@@ -1643,7 +1637,7 @@
       </c>
       <c r="C44" s="15">
         <f>C41-C37</f>
-        <v>-7.1171110913437283E-4</v>
+        <v>-6.4043360956804549E-4</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
@@ -1652,7 +1646,7 @@
       </c>
       <c r="C45" s="15">
         <f>C38+C44</f>
-        <v>4.8882888908656254E-3</v>
+        <v>4.9595663904319527E-3</v>
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="12"/>

--- a/Vanguard EU/Vanguard-ETFs-KostenBepaling2020.xlsx
+++ b/Vanguard EU/Vanguard-ETFs-KostenBepaling2020.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\Vanguard EU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerben\Google Drive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\Vanguard EU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2677A085-5C23-457B-AD71-35E3A5DEB25C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MarketCap" sheetId="7" r:id="rId1"/>
@@ -44,9 +44,9 @@
   <commentList>
     <comment ref="T11" authorId="0" shapeId="0" xr:uid="{3E3CE202-C5B9-4A92-B8D2-82C869CF6CF5}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     5,3% lek via trackerbelegger gepakt</t>
       </text>
     </comment>
@@ -399,10 +399,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Komma" xfId="2" builtinId="3"/>
-    <cellStyle name="Procent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Valuta" xfId="3" builtinId="4"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -783,7 +783,7 @@
       <c r="B10" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <f>D8+(F8*2.5%)</f>
         <v>5.1124409352383687E-3</v>
       </c>
